--- a/data/output/2025/evaluasi_96.xlsx
+++ b/data/output/2025/evaluasi_96.xlsx
@@ -5043,7 +5043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6713,18 +6713,382 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D60" t="n">
+        <v>6.243686145491922</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>17.17132345022567</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>31.64385905983665</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>61.54226608993214</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-23.39799306578837</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.7505573753361511</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>55.36141196950924</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>-12.4937193242299</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5.870722556514539</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-8.375040346107236</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.344621619644905</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>-7.628417726178522</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>-0.927883695630295</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>-3.596186076239321</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -6741,7 +7105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8747,18 +9111,354 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D72" t="n">
+        <v>8.636503930471974</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>-4.122663826348331</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>31.45436885072924</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>-20.95033967953527</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.40197726557099</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>18.21620930779341</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5.619514542953161</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>-7.071941963275305</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>-6.302277857224693</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>-16.36998526949039</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>-8.283326789638423</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>-1.148423513117298</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
         <v>4.141243974455371</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -8775,7 +9475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10137,20 +10837,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.559483214729977</v>
+        <v>0.8712718361356897</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -10165,18 +10865,494 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D50" t="n">
+        <v>-0.02990858360880128</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-42.93171256803511</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-26.16474103374224</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4.558981062745259</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-56.6721521867301</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-78.35490288167473</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>5.193290275805673</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-6.293768586795413</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-22.92356776050917</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-54.62566889053411</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.8250119183598</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1.924027566265677</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2.88202396336123</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2.507830425840635</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>8.008752928096817</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>6.291476765849267</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2.559483214729977</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>-2.895445287418266</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -10193,7 +11369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11471,18 +12647,382 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>13.27913568728938</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.77424167471308</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>84.93618614216456</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.07740070503302</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-16.89858449499048</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4.771098971135126</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7.862742105115716</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-5.499552278236668</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-15.91454298370517</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4127448800845926</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.6989641956790438</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2.151930933485004</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2.412803187942542</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>-2.755383201338632</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -11499,7 +13039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12525,20 +14065,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.438726691472275</v>
+        <v>0.05623874506805294</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -12553,18 +14093,382 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D38" t="n">
+        <v>-14.28371899932178</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>79.63928365054912</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-4.281503342414405</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-46.19603700276338</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>25.11655477551001</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.7188584281387334</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-20.06885345923861</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-17.36423582398013</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5410476058284547</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.5277521610784784</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3.413090048498463</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3.601840208907735</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3.438726691472275</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>2.473578106564084</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -12581,7 +14485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13747,20 +15651,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.986728682792176</v>
+        <v>3.443902036088746</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -13775,18 +15679,438 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D43" t="n">
+        <v>10.51090284987074</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.36999529833436</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4.752550161381765</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-7.930281603321529</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6.7811952921409</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4.177165431753125</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-3.972738157455222</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.266806717776884</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.4515865558560087</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-3.386161503169211</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-3.530028306401229</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.373284637560488</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.5562802451862163</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.492898164232089</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4.986728682792176</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>8.253118296311097</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -13803,7 +16127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15025,20 +17349,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.63784881831521</v>
+        <v>1.887485911463169</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -15053,18 +17377,634 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D45" t="n">
+        <v>35.24435214714887</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.89576039505422</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.732882130363234</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-1.459816934135809</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.8681763635373991</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1.890319004438792</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2.016156393929303</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.4904055819225534</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2.160436547366885</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1.868922245181697</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.4505115603201676</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-2.341130468093943</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.90832306657008</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-7.54281783610337</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2.46360091342315</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.793058360461525</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>9.086102957694566</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>7.422373208711187</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-0.6374036845177597</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.1446966137651069</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>6.160331869770896</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4.63784881831521</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>-6.766090970684601</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -15081,7 +18021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16555,18 +19495,578 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D53" t="n">
+        <v>4.928206249284926</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4.399094187902131</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>19.45747305328866</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6.378991823015919</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-2.727461687981658</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1.99446767825119</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1.795849645572718</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-6.614342206315609</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7.829797439199178</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1.419898265910089</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1.500822323681575</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.1646986399299485</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-2.718313371953006</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1.141699088978403</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1.644351976154214</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-2.699304547084749</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.3888061916289647</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.1511612313719279</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.03802403519974</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>4.728761587213088</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>9608</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak Jaya</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>16.45884179047678</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
